--- a/db/templates/inbound_delivery_default.xlsx
+++ b/db/templates/inbound_delivery_default.xlsx
@@ -29,7 +29,7 @@
     <t>{{vendor.postalCode}} {{vendor.city}}</t>
   </si>
   <si>
-    <t>VAT: {{vendor.vatin}}</t>
+    <t>Matricule fiscal: {{vendor.vatin}}</t>
   </si>
   <si>
     <t>{{vendor.email}} | {{vendor.phone}}</t>
@@ -65,7 +65,7 @@
     <t>{{organization.postalCode}} {{organization.city}}</t>
   </si>
   <si>
-    <t>VAT: {{organization.vatin}}</t>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
   </si>
   <si>
     <t>Product</t>

--- a/db/templates/inbound_delivery_default.xlsx
+++ b/db/templates/inbound_delivery_default.xlsx
@@ -7,18 +7,36 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Goods Receipt" sheetId="1" r:id="rId1"/>
+    <sheet name="Bon de réception" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Goods Receipt'!$1:$13</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Bon de réception'!$1:$11</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+  <si>
+    <t>{{organization.logo}}</t>
+  </si>
+  <si>
+    <t>{{organization.name}}</t>
+  </si>
+  <si>
+    <t>{{organization.street}} {{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}} {{organization.city}}</t>
+  </si>
+  <si>
+    <t>Tél : {{organization.phone}}</t>
+  </si>
+  <si>
+    <t>MF : {{organization.vatin}}</t>
+  </si>
   <si>
     <t>{{vendor.name}}</t>
   </si>
@@ -29,253 +47,247 @@
     <t>{{vendor.postalCode}} {{vendor.city}}</t>
   </si>
   <si>
-    <t>Matricule fiscal: {{vendor.vatin}}</t>
-  </si>
-  <si>
-    <t>{{vendor.email}} | {{vendor.phone}}</t>
-  </si>
-  <si>
-    <t>GOODS RECEIPT</t>
-  </si>
-  <si>
-    <t>Receipt number: {{inboundDelivery.number}}</t>
-  </si>
-  <si>
-    <t>Receipt date: {{inboundDelivery.date}}</t>
-  </si>
-  <si>
-    <t>Purchase order: {{inboundDelivery.purchaseOrder}}</t>
-  </si>
-  <si>
-    <t>Vendor delivery note: {{inboundDelivery.vendorDeliveryNote}}</t>
-  </si>
-  <si>
-    <t>Tracking number: {{inboundDelivery.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Received By</t>
-  </si>
-  <si>
-    <t>{{organization.name}}</t>
-  </si>
-  <si>
-    <t>{{organization.street}} {{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}} {{organization.city}}</t>
-  </si>
-  <si>
-    <t>Matricule fiscal: {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Product</t>
+    <t>Tel: {{vendor.phone}}</t>
+  </si>
+  <si>
+    <t>MF: {{vendor.vatin}}</t>
+  </si>
+  <si>
+    <t>Bon de réception N°: {{inboundDelivery.number}}</t>
+  </si>
+  <si>
+    <t>Date : {{inboundDelivery.date}}</t>
+  </si>
+  <si>
+    <t>Code</t>
+  </si>
+  <si>
+    <t>Désignation</t>
+  </si>
+  <si>
+    <t>Quantité</t>
+  </si>
+  <si>
+    <t>Unité</t>
+  </si>
+  <si>
+    <t>Coût U.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unit}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitCost}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Cachet et Signature</t>
+  </si>
+  <si>
+    <t>IBAN : {{organization.iban}}</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
   </si>
   <si>
     <t>Description</t>
   </si>
   <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Buyer logo — place alone in a cell to anchor the uploaded image there</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.number}}</t>
+  </si>
+  <si>
+    <t>Goods receipt number</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.date}}</t>
+  </si>
+  <si>
+    <t>Receipt date</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.purchaseOrder}}</t>
+  </si>
+  <si>
+    <t>Linked purchase order number, blank if unset</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.vendorDeliveryNote}}</t>
+  </si>
+  <si>
+    <t>Vendor's delivery note number, blank if unset</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Tracking number, blank if unset</t>
+  </si>
+  <si>
+    <t>Buyer company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Buyer VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Buyer email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Buyer phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Buyer website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Buyer street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Buyer house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Buyer postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Buyer city</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Buyer IBAN</t>
+  </si>
+  <si>
+    <t>Buyer bank name</t>
+  </si>
+  <si>
+    <t>Vendor name</t>
+  </si>
+  <si>
+    <t>{{vendor.vatin}}</t>
+  </si>
+  <si>
+    <t>Vendor VAT number</t>
+  </si>
+  <si>
+    <t>{{vendor.email}}</t>
+  </si>
+  <si>
+    <t>Vendor email</t>
+  </si>
+  <si>
+    <t>{{vendor.phone}}</t>
+  </si>
+  <si>
+    <t>Vendor phone</t>
+  </si>
+  <si>
+    <t>{{vendor.street}}</t>
+  </si>
+  <si>
+    <t>Vendor street</t>
+  </si>
+  <si>
+    <t>{{vendor.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Vendor house number</t>
+  </si>
+  <si>
+    <t>{{vendor.postalCode}}</t>
+  </si>
+  <si>
+    <t>Vendor postal code</t>
+  </si>
+  <si>
+    <t>{{vendor.city}}</t>
+  </si>
+  <si>
+    <t>Vendor city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Linked product's SKU</t>
+  </si>
+  <si>
+    <t>Line item description</t>
+  </si>
+  <si>
     <t>Quantity</t>
   </si>
   <si>
-    <t>Unit Cost</t>
-  </si>
-  <si>
-    <t>Line Total</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}} {{lineItems.unit}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitCost}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Notes: {{inboundDelivery.notes}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.number}}</t>
-  </si>
-  <si>
-    <t>Receipt number</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.date}}</t>
-  </si>
-  <si>
-    <t>Receipt date</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.purchaseOrder}}</t>
-  </si>
-  <si>
-    <t>Linked purchase order number, blank if unlinked</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.vendorDeliveryNote}}</t>
-  </si>
-  <si>
-    <t>Number on the vendor's own paperwork, blank if unset</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Carrier tracking number, blank if unset</t>
-  </si>
-  <si>
-    <t>Vendor company name, blank if unset</t>
-  </si>
-  <si>
-    <t>{{vendor.vatin}}</t>
-  </si>
-  <si>
-    <t>Vendor VAT number</t>
-  </si>
-  <si>
-    <t>{{vendor.email}}</t>
-  </si>
-  <si>
-    <t>Vendor email</t>
-  </si>
-  <si>
-    <t>{{vendor.phone}}</t>
-  </si>
-  <si>
-    <t>Vendor phone</t>
-  </si>
-  <si>
-    <t>{{vendor.street}}</t>
-  </si>
-  <si>
-    <t>Vendor street</t>
-  </si>
-  <si>
-    <t>{{vendor.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Vendor house number</t>
-  </si>
-  <si>
-    <t>{{vendor.postalCode}}</t>
-  </si>
-  <si>
-    <t>Vendor postal code</t>
-  </si>
-  <si>
-    <t>{{vendor.city}}</t>
-  </si>
-  <si>
-    <t>Vendor city</t>
-  </si>
-  <si>
-    <t>Buyer (your own) company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Buyer VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Buyer email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Buyer phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Buyer website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Buyer street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Buyer house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Buyer postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Buyer city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in any one cell of the row to repeat once per line item; that whole cell is blanked in the output</t>
-  </si>
-  <si>
-    <t>Linked product's SKU, blank on a free-text line or an unset SKU</t>
-  </si>
-  <si>
-    <t>Line item description</t>
-  </si>
-  <si>
-    <t>{{lineItems.quantity}}</t>
-  </si>
-  <si>
-    <t>Quantity received</t>
-  </si>
-  <si>
-    <t>{{lineItems.unit}}</t>
-  </si>
-  <si>
-    <t>Unit of measure (e.g. pcs, kg), blank if unset</t>
-  </si>
-  <si>
-    <t>Unit cost, formatted with currency — feeds average cost, not a customer price</t>
+    <t>Unit of measure, blank if unset</t>
+  </si>
+  <si>
+    <t>Unit cost, formatted with currency</t>
   </si>
   <si>
     <t>Quantity x unit cost, formatted with currency</t>
@@ -296,7 +308,7 @@
     <t>{{export.generatedDate}}</t>
   </si>
   <si>
-    <t>Date this file was exported (not the receipt's own date), in the organization's date format</t>
+    <t>Date this file was exported, in the organization's date format</t>
   </si>
   <si>
     <t>{{export.generatedTime}}</t>
@@ -308,14 +320,14 @@
     <t>&amp;P (page number) / &amp;N (total pages)</t>
   </si>
   <si>
-    <t>Native Excel/LibreOffice codes, not a {{}} placeholder — only work inside this sheet's own Page Layout ▸ Header/Footer, never in a regular cell, since the page count isn't known until export. The default footer already shows "Page &amp;P of &amp;N" on every page; edit it in Excel/LibreOffice's own header/footer editor to move or restyle it</t>
+    <t>Native Excel/LibreOffice codes, only work in Page Layout ▸ Header/Footer</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -336,13 +348,19 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="12"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
       <color/>
       <sz val="14"/>
+    </font>
+    <font>
+      <family val="2"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
@@ -359,16 +377,16 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1E293B"/>
+        <fgColor rgb="FFE2E8F0"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE2E8F0"/>
+        <fgColor rgb="FF1E293B"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -376,11 +394,25 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF808080"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF808080"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF808080"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF808080"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -388,22 +420,34 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="true" applyFill="true" applyBorder="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
   </cellXfs>
@@ -679,124 +723,162 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="22"/>
-    <col customWidth="true" max="2" min="2" width="40"/>
-    <col customWidth="true" max="5" min="3" width="14"/>
+    <col customWidth="true" max="1" min="1" width="14"/>
+    <col customWidth="true" max="2" min="2" width="34"/>
+    <col customWidth="true" max="6" min="3" width="16"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="E1" s="2" t="s">
-        <v>5</v>
-      </c>
+      <c r="C1" s="7" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="C2" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="E2" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
+      <c r="C3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>3</v>
-      </c>
-      <c r="E4" t="s">
-        <v>8</v>
-      </c>
+        <v>2</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
     </row>
     <row r="5">
       <c r="A5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="s">
         <v>4</v>
       </c>
-      <c r="E5" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="s">
+      <c r="A7" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="C8" s="7" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="s">
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9">
+      <c r="C9" s="7"/>
+      <c r="D9" s="7" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="s">
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="s">
+      <c r="B11" s="4" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="s">
+      <c r="C11" s="4" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="s">
+      <c r="D11" s="4" t="s">
         <v>16</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="E11" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="F11" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="D13" s="3" t="s">
+    </row>
+    <row r="12">
+      <c r="A12" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="B12" s="7" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="s">
+      <c r="C12" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="B14" t="s">
+      <c r="D12" s="7" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="F12" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="J12" t="s">
         <v>25</v>
       </c>
-      <c r="F14" t="s">
+    </row>
+    <row r="18">
+      <c r="D18" s="8" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" t="s">
+    <row r="22">
+      <c r="A22" t="s">
         <v>27</v>
       </c>
+      <c r="D22" t="s">
+        <v>28</v>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="10">
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="C2:F2"/>
+    <mergeCell ref="C3:F3"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C8:F8"/>
+    <mergeCell ref="D9:F9"/>
+    <mergeCell ref="D18:G18"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="D22:G22"/>
+  </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
@@ -815,178 +897,178 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="5" t="s">
-        <v>28</v>
+      <c r="A1" s="9" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="8" t="s">
-        <v>29</v>
+      <c r="A2" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="s">
-        <v>30</v>
-      </c>
-      <c r="B4" s="6" t="s">
+      <c r="A4" s="10" t="s">
         <v>31</v>
       </c>
-      <c r="C4" s="6" t="s">
-        <v>17</v>
+      <c r="B4" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" s="10" t="s">
+        <v>33</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="s">
-        <v>32</v>
+      <c r="A5" s="11" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>33</v>
+        <v>0</v>
       </c>
       <c r="C6" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C7" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C8" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C9" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C11" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="C12" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>46</v>
+        <v>1</v>
       </c>
       <c r="C13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C14" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C17" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C18" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
-        <v>12</v>
+        <v>61</v>
       </c>
       <c r="C20" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C21" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C22" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="C23" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>67</v>
+        <v>6</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
@@ -1025,115 +1107,139 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="7" t="s">
+      <c r="B29" t="s">
         <v>77</v>
+      </c>
+      <c r="C29" t="s">
+        <v>78</v>
       </c>
     </row>
     <row r="30">
       <c r="B30" t="s">
-        <v>26</v>
+        <v>79</v>
       </c>
       <c r="C30" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
     </row>
     <row r="31">
       <c r="B31" t="s">
-        <v>21</v>
+        <v>81</v>
       </c>
       <c r="C31" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="32">
-      <c r="B32" t="s">
-        <v>22</v>
-      </c>
-      <c r="C32" t="s">
-        <v>80</v>
+      <c r="A32" s="11" t="s">
+        <v>83</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>81</v>
+        <v>25</v>
       </c>
       <c r="C33" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>83</v>
+        <v>19</v>
       </c>
       <c r="C34" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="C35" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C36" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="7" t="s">
-        <v>87</v>
+      <c r="B37" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>88</v>
+        <v>23</v>
       </c>
       <c r="C38" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="7" t="s">
+      <c r="B39" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="40">
-      <c r="B40" t="s">
+      <c r="A40" s="11" t="s">
         <v>91</v>
-      </c>
-      <c r="C40" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
+        <v>92</v>
+      </c>
+      <c r="C41" t="s">
         <v>93</v>
       </c>
-      <c r="C41" t="s">
+    </row>
+    <row r="42">
+      <c r="A42" s="11" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="42">
-      <c r="B42" t="s">
+    <row r="43">
+      <c r="B43" t="s">
         <v>95</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C43" t="s">
         <v>96</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="s">
+        <v>97</v>
+      </c>
+      <c r="C44" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="B45" t="s">
+        <v>99</v>
+      </c>
+      <c r="C45" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A29:C29"/>
-    <mergeCell ref="A37:C37"/>
-    <mergeCell ref="A39:C39"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A40:C40"/>
+    <mergeCell ref="A42:C42"/>
   </mergeCells>
 </worksheet>
 </file>
--- a/db/templates/inbound_delivery_default.xlsx
+++ b/db/templates/inbound_delivery_default.xlsx
@@ -7,281 +7,284 @@
     <workbookView xWindow="0" yWindow="0" windowWidth="14805" windowHeight="8010"/>
   </bookViews>
   <sheets>
-    <sheet name="Bon de réception" sheetId="1" r:id="rId1"/>
+    <sheet name="Goods Receipt" sheetId="1" r:id="rId1"/>
     <sheet name="Available fields" sheetId="2" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Bon de réception'!$1:$11</definedName>
+    <definedName localSheetId="0" name="_xlnm.Print_Titles">'Goods Receipt'!$1:$13</definedName>
   </definedNames>
   <calcPr calcId="122211"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="102" uniqueCount="102">
+  <si>
+    <t>{{vendor.name}}</t>
+  </si>
+  <si>
+    <t>{{vendor.street}} {{vendor.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{vendor.postalCode}} {{vendor.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{vendor.vatin}}</t>
+  </si>
+  <si>
+    <t>{{vendor.email}} | {{vendor.phone}}</t>
+  </si>
+  <si>
+    <t>GOODS RECEIPT</t>
+  </si>
+  <si>
+    <t>Receipt number: {{inboundDelivery.number}}</t>
+  </si>
+  <si>
+    <t>Receipt date: {{inboundDelivery.date}}</t>
+  </si>
+  <si>
+    <t>Purchase order: {{inboundDelivery.purchaseOrder}}</t>
+  </si>
+  <si>
+    <t>Vendor delivery note: {{inboundDelivery.vendorDeliveryNote}}</t>
+  </si>
+  <si>
+    <t>Tracking number: {{inboundDelivery.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Received By</t>
+  </si>
+  <si>
+    <t>{{organization.name}}</t>
+  </si>
+  <si>
+    <t>{{organization.street}} {{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}} {{organization.city}}</t>
+  </si>
+  <si>
+    <t>Matricule fiscal: {{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Product</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>Quantity</t>
+  </si>
+  <si>
+    <t>Unit Cost</t>
+  </si>
+  <si>
+    <t>Line Total</t>
+  </si>
+  <si>
+    <t>{{lineItems.sku}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.description}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.quantity}} {{lineItems.unit}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.unitCost}}</t>
+  </si>
+  <si>
+    <t>{{lineItems.lineTotal}}</t>
+  </si>
+  <si>
+    <t>{{#lineItems}}</t>
+  </si>
+  <si>
+    <t>Notes: {{inboundDelivery.notes}}</t>
+  </si>
+  <si>
+    <t>Available template placeholders</t>
+  </si>
+  <si>
+    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
+  </si>
+  <si>
+    <t>Group</t>
+  </si>
+  <si>
+    <t>Placeholder</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
   <si>
     <t>{{organization.logo}}</t>
   </si>
   <si>
-    <t>{{organization.name}}</t>
-  </si>
-  <si>
-    <t>{{organization.street}} {{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}} {{organization.city}}</t>
-  </si>
-  <si>
-    <t>Tél : {{organization.phone}}</t>
-  </si>
-  <si>
-    <t>MF : {{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>{{vendor.name}}</t>
-  </si>
-  <si>
-    <t>{{vendor.street}} {{vendor.houseNumber}}</t>
-  </si>
-  <si>
-    <t>{{vendor.postalCode}} {{vendor.city}}</t>
-  </si>
-  <si>
-    <t>Tel: {{vendor.phone}}</t>
-  </si>
-  <si>
-    <t>MF: {{vendor.vatin}}</t>
-  </si>
-  <si>
-    <t>Bon de réception N°: {{inboundDelivery.number}}</t>
-  </si>
-  <si>
-    <t>Date : {{inboundDelivery.date}}</t>
-  </si>
-  <si>
-    <t>Code</t>
-  </si>
-  <si>
-    <t>Désignation</t>
-  </si>
-  <si>
-    <t>Quantité</t>
-  </si>
-  <si>
-    <t>Unité</t>
-  </si>
-  <si>
-    <t>Coût U.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
-  </si>
-  <si>
-    <t>{{lineItems.sku}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.description}}</t>
+    <t>Buyer logo — place alone in a cell to anchor the uploaded image there</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.number}}</t>
+  </si>
+  <si>
+    <t>Goods receipt number</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.date}}</t>
+  </si>
+  <si>
+    <t>Receipt date</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.currency}}</t>
+  </si>
+  <si>
+    <t>Currency code (e.g. EUR)</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.purchaseOrder}}</t>
+  </si>
+  <si>
+    <t>Linked purchase order number, blank if unset</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.vendorDeliveryNote}}</t>
+  </si>
+  <si>
+    <t>Vendor's delivery note number, blank if unset</t>
+  </si>
+  <si>
+    <t>{{inboundDelivery.trackingNumber}}</t>
+  </si>
+  <si>
+    <t>Tracking number, blank if unset</t>
+  </si>
+  <si>
+    <t>Buyer company name</t>
+  </si>
+  <si>
+    <t>{{organization.vatin}}</t>
+  </si>
+  <si>
+    <t>Buyer VAT number</t>
+  </si>
+  <si>
+    <t>{{organization.email}}</t>
+  </si>
+  <si>
+    <t>Buyer email</t>
+  </si>
+  <si>
+    <t>{{organization.phone}}</t>
+  </si>
+  <si>
+    <t>Buyer phone</t>
+  </si>
+  <si>
+    <t>{{organization.website}}</t>
+  </si>
+  <si>
+    <t>Buyer website</t>
+  </si>
+  <si>
+    <t>{{organization.street}}</t>
+  </si>
+  <si>
+    <t>Buyer street</t>
+  </si>
+  <si>
+    <t>{{organization.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Buyer house number</t>
+  </si>
+  <si>
+    <t>{{organization.postalCode}}</t>
+  </si>
+  <si>
+    <t>Buyer postal code</t>
+  </si>
+  <si>
+    <t>{{organization.city}}</t>
+  </si>
+  <si>
+    <t>Buyer city</t>
+  </si>
+  <si>
+    <t>{{organization.iban}}</t>
+  </si>
+  <si>
+    <t>Buyer IBAN</t>
+  </si>
+  <si>
+    <t>{{organization.bankName}}</t>
+  </si>
+  <si>
+    <t>Buyer bank name</t>
+  </si>
+  <si>
+    <t>Vendor name</t>
+  </si>
+  <si>
+    <t>{{vendor.vatin}}</t>
+  </si>
+  <si>
+    <t>Vendor VAT number</t>
+  </si>
+  <si>
+    <t>{{vendor.email}}</t>
+  </si>
+  <si>
+    <t>Vendor email</t>
+  </si>
+  <si>
+    <t>{{vendor.phone}}</t>
+  </si>
+  <si>
+    <t>Vendor phone</t>
+  </si>
+  <si>
+    <t>{{vendor.street}}</t>
+  </si>
+  <si>
+    <t>Vendor street</t>
+  </si>
+  <si>
+    <t>{{vendor.houseNumber}}</t>
+  </si>
+  <si>
+    <t>Vendor house number</t>
+  </si>
+  <si>
+    <t>{{vendor.postalCode}}</t>
+  </si>
+  <si>
+    <t>Vendor postal code</t>
+  </si>
+  <si>
+    <t>{{vendor.city}}</t>
+  </si>
+  <si>
+    <t>Vendor city</t>
+  </si>
+  <si>
+    <t>Item lines</t>
+  </si>
+  <si>
+    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
+  </si>
+  <si>
+    <t>Linked product's SKU</t>
+  </si>
+  <si>
+    <t>Line item description</t>
   </si>
   <si>
     <t>{{lineItems.quantity}}</t>
   </si>
   <si>
     <t>{{lineItems.unit}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.unitCost}}</t>
-  </si>
-  <si>
-    <t>{{lineItems.lineTotal}}</t>
-  </si>
-  <si>
-    <t>{{#lineItems}}</t>
-  </si>
-  <si>
-    <t>Cachet et Signature</t>
-  </si>
-  <si>
-    <t>IBAN : {{organization.iban}}</t>
-  </si>
-  <si>
-    <t>{{organization.bankName}}</t>
-  </si>
-  <si>
-    <t>Available template placeholders</t>
-  </si>
-  <si>
-    <t>Use {{placeholder}} in any cell. An unresolved one is left blank in the export, never an error.</t>
-  </si>
-  <si>
-    <t>Group</t>
-  </si>
-  <si>
-    <t>Placeholder</t>
-  </si>
-  <si>
-    <t>Description</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>Buyer logo — place alone in a cell to anchor the uploaded image there</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.number}}</t>
-  </si>
-  <si>
-    <t>Goods receipt number</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.date}}</t>
-  </si>
-  <si>
-    <t>Receipt date</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.currency}}</t>
-  </si>
-  <si>
-    <t>Currency code (e.g. EUR)</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.purchaseOrder}}</t>
-  </si>
-  <si>
-    <t>Linked purchase order number, blank if unset</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.vendorDeliveryNote}}</t>
-  </si>
-  <si>
-    <t>Vendor's delivery note number, blank if unset</t>
-  </si>
-  <si>
-    <t>{{inboundDelivery.trackingNumber}}</t>
-  </si>
-  <si>
-    <t>Tracking number, blank if unset</t>
-  </si>
-  <si>
-    <t>Buyer company name</t>
-  </si>
-  <si>
-    <t>{{organization.vatin}}</t>
-  </si>
-  <si>
-    <t>Buyer VAT number</t>
-  </si>
-  <si>
-    <t>{{organization.email}}</t>
-  </si>
-  <si>
-    <t>Buyer email</t>
-  </si>
-  <si>
-    <t>{{organization.phone}}</t>
-  </si>
-  <si>
-    <t>Buyer phone</t>
-  </si>
-  <si>
-    <t>{{organization.website}}</t>
-  </si>
-  <si>
-    <t>Buyer website</t>
-  </si>
-  <si>
-    <t>{{organization.street}}</t>
-  </si>
-  <si>
-    <t>Buyer street</t>
-  </si>
-  <si>
-    <t>{{organization.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Buyer house number</t>
-  </si>
-  <si>
-    <t>{{organization.postalCode}}</t>
-  </si>
-  <si>
-    <t>Buyer postal code</t>
-  </si>
-  <si>
-    <t>{{organization.city}}</t>
-  </si>
-  <si>
-    <t>Buyer city</t>
-  </si>
-  <si>
-    <t>{{organization.iban}}</t>
-  </si>
-  <si>
-    <t>Buyer IBAN</t>
-  </si>
-  <si>
-    <t>Buyer bank name</t>
-  </si>
-  <si>
-    <t>Vendor name</t>
-  </si>
-  <si>
-    <t>{{vendor.vatin}}</t>
-  </si>
-  <si>
-    <t>Vendor VAT number</t>
-  </si>
-  <si>
-    <t>{{vendor.email}}</t>
-  </si>
-  <si>
-    <t>Vendor email</t>
-  </si>
-  <si>
-    <t>{{vendor.phone}}</t>
-  </si>
-  <si>
-    <t>Vendor phone</t>
-  </si>
-  <si>
-    <t>{{vendor.street}}</t>
-  </si>
-  <si>
-    <t>Vendor street</t>
-  </si>
-  <si>
-    <t>{{vendor.houseNumber}}</t>
-  </si>
-  <si>
-    <t>Vendor house number</t>
-  </si>
-  <si>
-    <t>{{vendor.postalCode}}</t>
-  </si>
-  <si>
-    <t>Vendor postal code</t>
-  </si>
-  <si>
-    <t>{{vendor.city}}</t>
-  </si>
-  <si>
-    <t>Vendor city</t>
-  </si>
-  <si>
-    <t>Item lines</t>
-  </si>
-  <si>
-    <t>Marker (not a value) — place alone in one cell of the row to repeat once per line item</t>
-  </si>
-  <si>
-    <t>Linked product's SKU</t>
-  </si>
-  <si>
-    <t>Line item description</t>
-  </si>
-  <si>
-    <t>Quantity</t>
   </si>
   <si>
     <t>Unit of measure, blank if unset</t>
@@ -354,13 +357,13 @@
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color/>
-      <sz val="14"/>
+      <color rgb="FFFFFFFF"/>
     </font>
     <font>
       <family val="2"/>
       <b val="1"/>
-      <color rgb="FFFFFFFF"/>
+      <color/>
+      <sz val="14"/>
     </font>
     <font>
       <family val="2"/>
@@ -412,7 +415,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
@@ -438,10 +441,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
       <alignment/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
       <alignment/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="false">
@@ -723,162 +729,124 @@
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col customWidth="true" max="1" min="1" width="14"/>
-    <col customWidth="true" max="2" min="2" width="34"/>
-    <col customWidth="true" max="6" min="3" width="16"/>
+    <col customWidth="true" max="1" min="1" width="22"/>
+    <col customWidth="true" max="2" min="2" width="40"/>
+    <col customWidth="true" max="5" min="3" width="14"/>
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="E1" s="2" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+      <c r="E2" t="s">
         <v>6</v>
       </c>
-      <c r="D1" s="7"/>
-      <c r="E1" s="7"/>
-      <c r="F1" s="7"/>
-    </row>
-    <row r="2">
-      <c r="C2" s="7" t="s">
+    </row>
+    <row r="3">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="D3" s="7"/>
-      <c r="E3" s="7"/>
-      <c r="F3" s="7"/>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>2</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
+        <v>3</v>
+      </c>
+      <c r="E4" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>3</v>
-      </c>
-      <c r="C5" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="E5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="E6" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="7"/>
-      <c r="E5" s="7"/>
-      <c r="F5" s="7"/>
-    </row>
-    <row r="6">
-      <c r="A6" t="s">
-        <v>4</v>
-      </c>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
     </row>
     <row r="7">
-      <c r="A7" t="s">
-        <v>5</v>
+      <c r="A7" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
     <row r="8">
-      <c r="C8" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
+      <c r="A8" t="s">
+        <v>12</v>
+      </c>
     </row>
     <row r="9">
-      <c r="C9" s="7"/>
-      <c r="D9" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
+      <c r="A9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="11">
-      <c r="A11" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="C11" s="4" t="s">
+      <c r="A11" t="s">
         <v>15</v>
       </c>
-      <c r="D11" s="4" t="s">
+    </row>
+    <row r="13">
+      <c r="A13" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="B13" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="C13" s="9" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="D13" s="9" t="s">
         <v>19</v>
       </c>
-      <c r="B12" s="7" t="s">
+      <c r="E13" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="5" t="s">
+    </row>
+    <row r="14">
+      <c r="A14" t="s">
         <v>21</v>
       </c>
-      <c r="D12" s="7" t="s">
+      <c r="B14" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="5" t="s">
+      <c r="C14" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="D14" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="J12" t="s">
+      <c r="E14" s="5" t="s">
         <v>25</v>
       </c>
+      <c r="F14" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="18">
-      <c r="D18" s="8" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="s">
+      <c r="A18" t="s">
         <v>27</v>
       </c>
-      <c r="D22" t="s">
-        <v>28</v>
-      </c>
     </row>
   </sheetData>
-  <mergeCells count="10">
-    <mergeCell ref="C1:F1"/>
-    <mergeCell ref="C2:F2"/>
-    <mergeCell ref="C3:F3"/>
-    <mergeCell ref="C4:F4"/>
-    <mergeCell ref="C5:F5"/>
-    <mergeCell ref="C8:F8"/>
-    <mergeCell ref="D9:F9"/>
-    <mergeCell ref="D18:G18"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="D22:G22"/>
-  </mergeCells>
   <pageSetup fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddFooter>&amp;CPage &amp;P of &amp;N</oddFooter>
@@ -897,170 +865,170 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="13" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" s="12" t="s">
+    <row r="4">
+      <c r="A4" s="11" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="C4" s="11" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="12" t="s">
         <v>32</v>
-      </c>
-      <c r="C4" s="10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="11" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="6">
       <c r="B6" t="s">
-        <v>0</v>
+        <v>33</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="s">
+        <v>35</v>
+      </c>
+      <c r="C7" t="s">
         <v>36</v>
-      </c>
-      <c r="C7" t="s">
-        <v>37</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="s">
+        <v>37</v>
+      </c>
+      <c r="C8" t="s">
         <v>38</v>
-      </c>
-      <c r="C8" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="s">
+        <v>39</v>
+      </c>
+      <c r="C9" t="s">
         <v>40</v>
-      </c>
-      <c r="C9" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" t="s">
         <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" t="s">
         <v>44</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
       </c>
     </row>
     <row r="12">
       <c r="B12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C12" t="s">
         <v>46</v>
-      </c>
-      <c r="C12" t="s">
-        <v>47</v>
       </c>
     </row>
     <row r="13">
       <c r="B13" t="s">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="C13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" t="s">
+        <v>48</v>
+      </c>
+      <c r="C14" t="s">
         <v>49</v>
-      </c>
-      <c r="C14" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="15">
       <c r="B15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C15" t="s">
         <v>51</v>
-      </c>
-      <c r="C15" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C16" t="s">
         <v>53</v>
-      </c>
-      <c r="C16" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="17">
       <c r="B17" t="s">
+        <v>54</v>
+      </c>
+      <c r="C17" t="s">
         <v>55</v>
-      </c>
-      <c r="C17" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="18">
       <c r="B18" t="s">
+        <v>56</v>
+      </c>
+      <c r="C18" t="s">
         <v>57</v>
-      </c>
-      <c r="C18" t="s">
-        <v>58</v>
       </c>
     </row>
     <row r="19">
       <c r="B19" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" t="s">
         <v>59</v>
-      </c>
-      <c r="C19" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="20">
       <c r="B20" t="s">
+        <v>60</v>
+      </c>
+      <c r="C20" t="s">
         <v>61</v>
-      </c>
-      <c r="C20" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="21">
       <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
         <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="22">
       <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
         <v>65</v>
-      </c>
-      <c r="C22" t="s">
-        <v>66</v>
       </c>
     </row>
     <row r="23">
       <c r="B23" t="s">
-        <v>28</v>
+        <v>66</v>
       </c>
       <c r="C23" t="s">
         <v>67</v>
@@ -1068,7 +1036,7 @@
     </row>
     <row r="24">
       <c r="B24" t="s">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="C24" t="s">
         <v>68</v>
@@ -1131,13 +1099,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="11" t="s">
+      <c r="A32" s="12" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="33">
       <c r="B33" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C33" t="s">
         <v>84</v>
@@ -1145,7 +1113,7 @@
     </row>
     <row r="34">
       <c r="B34" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C34" t="s">
         <v>85</v>
@@ -1153,7 +1121,7 @@
     </row>
     <row r="35">
       <c r="B35" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C35" t="s">
         <v>86</v>
@@ -1161,76 +1129,76 @@
     </row>
     <row r="36">
       <c r="B36" t="s">
-        <v>21</v>
+        <v>87</v>
       </c>
       <c r="C36" t="s">
-        <v>87</v>
+        <v>18</v>
       </c>
     </row>
     <row r="37">
       <c r="B37" t="s">
-        <v>22</v>
+        <v>88</v>
       </c>
       <c r="C37" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="38">
       <c r="B38" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
     </row>
     <row r="39">
       <c r="B39" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C39" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="11" t="s">
-        <v>91</v>
+      <c r="A40" s="12" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="41">
       <c r="B41" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="11" t="s">
-        <v>94</v>
+      <c r="A42" s="12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="43">
       <c r="B43" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C43" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
     </row>
     <row r="44">
       <c r="B44" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C44" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="45">
       <c r="B45" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C45" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
     </row>
   </sheetData>
